--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484800_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484800_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9836</v>
+        <v>3.6415</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4056</v>
+        <v>1.6719</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5781</v>
+        <v>1.9696</v>
       </c>
       <c r="G2" t="n">
         <v>-0.8598</v>
@@ -610,13 +610,13 @@
         <v>2.8305</v>
       </c>
       <c r="S2" t="n">
-        <v>3.4859</v>
+        <v>1.1438</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3936</v>
+        <v>0.6599</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0924</v>
+        <v>0.4839</v>
       </c>
       <c r="V2" t="n">
         <v>7.1314</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8117</v>
+        <v>1.3215</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.825</v>
+        <v>-0.4739</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6367</v>
+        <v>1.7954</v>
       </c>
       <c r="G4" t="n">
         <v>-0.0613</v>
@@ -766,13 +766,13 @@
         <v>1.5096</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6366000000000001</v>
+        <v>-0.1268</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4456</v>
+        <v>-0.0945</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.191</v>
+        <v>-0.0323</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. LEON LAFUENTE</t>
+          <t>J. NUNEZ NIEVAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1299</v>
+        <v>0.4916</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-1.4688</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1299</v>
+        <v>1.9603</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1299</v>
+        <v>-0.7683</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.1064</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1299</v>
+        <v>-0.8748</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-0.4089</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.2066</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0.6155</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1299</v>
+        <v>-0.3594</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-0.1001</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1299</v>
+        <v>-0.2593</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.7548</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.6418</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0.7401</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-0.4181</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0.322</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. DIAZ MUNOZ</t>
+          <t>K. LEON LAFUENTE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0377</v>
+        <v>0.1299</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0377</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.1299</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0211</v>
+        <v>0.1299</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0211</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.1299</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0211</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0211</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.1299</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.1299</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -922,10 +922,10 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0588</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0588</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. NUNEZ NIEVAS</t>
+          <t>P. DIAZ MUNOZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3538</v>
+        <v>-0.0377</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.9173</v>
+        <v>-0.0377</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5635</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7683</v>
+        <v>0.0211</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1064</v>
+        <v>0.0211</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8748</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4089</v>
+        <v>0.0211</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2066</v>
+        <v>0.0211</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6155</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3594</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1001</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2593</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7548</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.6418</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.5854</v>
+        <v>-0.0588</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8666</v>
+        <v>-0.0588</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7189</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8848</v>
+        <v>-0.8319</v>
       </c>
       <c r="E8" t="n">
         <v>-0.746</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1388</v>
+        <v>-0.0859</v>
       </c>
       <c r="G8" t="n">
         <v>-0.8613</v>
@@ -1078,13 +1078,13 @@
         <v>0.1887</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2122</v>
+        <v>-0.1593</v>
       </c>
       <c r="T8" t="n">
         <v>-0.1176</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0946</v>
+        <v>-0.0417</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1696</v>
+        <v>-1.4062</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.326</v>
+        <v>-2.7212</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1564</v>
+        <v>1.3151</v>
       </c>
       <c r="G10" t="n">
         <v>-0.8879</v>
@@ -1234,13 +1234,13 @@
         <v>2.2644</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3573</v>
+        <v>-0.5939</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0458</v>
+        <v>-0.4411</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3115</v>
+        <v>-0.1528</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3018</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.61</v>
+        <v>-3.0195</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.4221</v>
+        <v>-2.7787</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1879</v>
+        <v>-0.2408</v>
       </c>
       <c r="G11" t="n">
         <v>-1.9001</v>
@@ -1312,13 +1312,13 @@
         <v>3.0192</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6725</v>
+        <v>-0.082</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9254</v>
+        <v>-0.282</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2529</v>
+        <v>0.2</v>
       </c>
       <c r="V11" t="n">
         <v>-2.1696</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.8916</v>
+        <v>-4.2612</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7343</v>
+        <v>-2.1039</v>
       </c>
       <c r="F12" t="n">
         <v>-2.1572</v>
@@ -1390,10 +1390,10 @@
         <v>1.887</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8041</v>
+        <v>0.4346</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6089</v>
+        <v>0.2393</v>
       </c>
       <c r="U12" t="n">
         <v>0.1952</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.8087</v>
+        <v>-4.2711</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.4851</v>
+        <v>-1.8417</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.3236</v>
+        <v>-2.4294</v>
       </c>
       <c r="G13" t="n">
         <v>-1.9711</v>
@@ -1468,13 +1468,13 @@
         <v>0.7548</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4603</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7396</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2793</v>
+        <v>0.1735</v>
       </c>
       <c r="V13" t="n">
         <v>-2.1886</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-8.4937</v>
+        <v>-7.9058</v>
       </c>
       <c r="E14" t="n">
-        <v>-10.5393</v>
+        <v>-9.9514</v>
       </c>
       <c r="F14" t="n">
-        <v>2.045799999999999</v>
+        <v>2.0457</v>
       </c>
       <c r="G14" t="n">
         <v>-6.9321</v>
@@ -1516,7 +1516,7 @@
         <v>-6.1747</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.7574999999999994</v>
+        <v>-0.7574999999999998</v>
       </c>
       <c r="J14" t="n">
         <v>-2.5072</v>
@@ -1546,10 +1546,10 @@
         <v>15.096</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8817999999999995</v>
+        <v>-0.2939</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2557</v>
+        <v>-0.6678999999999998</v>
       </c>
       <c r="U14" t="n">
         <v>0.3739</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.2621</v>
+        <v>7.6133</v>
       </c>
       <c r="E15" t="n">
-        <v>4.7283</v>
+        <v>4.9231</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5338</v>
+        <v>2.6902</v>
       </c>
       <c r="G15" t="n">
         <v>4.657</v>
@@ -1624,13 +1624,13 @@
         <v>3.0192</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2651</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0407</v>
+        <v>0.1542</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3058</v>
+        <v>0.4621</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3018</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.916</v>
+        <v>1.8395</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7836</v>
+        <v>-1.8554</v>
       </c>
       <c r="F16" t="n">
-        <v>3.6997</v>
+        <v>3.695</v>
       </c>
       <c r="G16" t="n">
         <v>1.2424</v>
@@ -1702,13 +1702,13 @@
         <v>1.887</v>
       </c>
       <c r="S16" t="n">
-        <v>1.8623</v>
+        <v>0.7858000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1968</v>
+        <v>0.125</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6655</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8849</v>
+        <v>1.6115</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0015</v>
+        <v>0.781</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8834</v>
+        <v>0.8305</v>
       </c>
       <c r="G17" t="n">
         <v>3.4941</v>
@@ -1780,13 +1780,13 @@
         <v>2.6418</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6848</v>
+        <v>0.0417</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1046</v>
+        <v>-0.3252</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4198</v>
+        <v>0.3669</v>
       </c>
       <c r="V17" t="n">
         <v>-2.4904</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6844</v>
+        <v>0.6893</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.8738</v>
+        <v>-1.679</v>
       </c>
       <c r="F18" t="n">
-        <v>2.5582</v>
+        <v>2.3683</v>
       </c>
       <c r="G18" t="n">
         <v>-0.8096</v>
@@ -1858,13 +1858,13 @@
         <v>3.2079</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5697</v>
+        <v>0.5746</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4645</v>
+        <v>-0.2696</v>
       </c>
       <c r="U18" t="n">
-        <v>1.0342</v>
+        <v>0.8443000000000001</v>
       </c>
       <c r="V18" t="n">
         <v>1.8678</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0388</v>
+        <v>0.4838</v>
       </c>
       <c r="E19" t="n">
         <v>-0.6368</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6756</v>
+        <v>1.1206</v>
       </c>
       <c r="G19" t="n">
         <v>1.0262</v>
@@ -1936,13 +1936,13 @@
         <v>1.1322</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3839</v>
+        <v>0.0611</v>
       </c>
       <c r="T19" t="n">
         <v>0.0152</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3991</v>
+        <v>0.0459</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6036</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. RUIZ FRANCO</t>
+          <t>S. GALVEZ ARROYO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.36</v>
+        <v>0.2854</v>
       </c>
       <c r="E20" t="n">
-        <v>0.224</v>
+        <v>-2.4986</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.584</v>
+        <v>2.784</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.8955</v>
+        <v>2.1988</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6552</v>
+        <v>-0.3232</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2403</v>
+        <v>2.522</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8988</v>
+        <v>0.9718</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9399</v>
+        <v>-0.9869</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0411</v>
+        <v>1.9587</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9967</v>
+        <v>1.227</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7153</v>
+        <v>0.6637</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2814</v>
+        <v>0.5633</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3774</v>
+        <v>-1.6983</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-5.0949</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3774</v>
+        <v>3.3966</v>
       </c>
       <c r="S20" t="n">
-        <v>1.158</v>
+        <v>0.4075</v>
       </c>
       <c r="T20" t="n">
-        <v>1.1228</v>
+        <v>-0.2433</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0353</v>
+        <v>0.6508</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.6226</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.8678</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.4904</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3805</v>
+        <v>-0.2784</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1249</v>
+        <v>-0.4172</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2557</v>
+        <v>0.1388</v>
       </c>
       <c r="G21" t="n">
         <v>-1.5793</v>
@@ -2092,13 +2092,13 @@
         <v>1.1322</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9899</v>
+        <v>-0.8878</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0029</v>
+        <v>-0.2894</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9928</v>
+        <v>-0.5984</v>
       </c>
       <c r="V21" t="n">
         <v>1.2452</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4281</v>
+        <v>-0.3836</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6425999999999999</v>
+        <v>-0.5452</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2145</v>
+        <v>0.1616</v>
       </c>
       <c r="G22" t="n">
         <v>-0.7579</v>
@@ -2170,13 +2170,13 @@
         <v>0.1887</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1411</v>
+        <v>0.1856</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1176</v>
+        <v>-0.0201</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2587</v>
+        <v>0.2058</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. GALVEZ ARROYO</t>
+          <t>D. RUIZ FRANCO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.7647</v>
+        <v>-0.8917</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1807</v>
+        <v>-0.3606</v>
       </c>
       <c r="F23" t="n">
-        <v>2.416</v>
+        <v>-0.5311</v>
       </c>
       <c r="G23" t="n">
-        <v>2.1988</v>
+        <v>-1.8955</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3232</v>
+        <v>-1.6552</v>
       </c>
       <c r="I23" t="n">
-        <v>2.522</v>
+        <v>-0.2403</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9718</v>
+        <v>-0.8988</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.9869</v>
+        <v>-0.9399</v>
       </c>
       <c r="L23" t="n">
-        <v>1.9587</v>
+        <v>0.0411</v>
       </c>
       <c r="M23" t="n">
-        <v>1.227</v>
+        <v>-0.9967</v>
       </c>
       <c r="N23" t="n">
-        <v>0.6637</v>
+        <v>-0.7153</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5633</v>
+        <v>-0.2814</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.6983</v>
+        <v>0.3774</v>
       </c>
       <c r="Q23" t="n">
-        <v>-5.0949</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.3966</v>
+        <v>0.3774</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6425</v>
+        <v>0.6263</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9254</v>
+        <v>0.5382</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2828</v>
+        <v>0.0882</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6226</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.8678</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.4904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.3592</v>
+        <v>-1.1764</v>
       </c>
       <c r="E24" t="n">
         <v>-0.0588</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3004</v>
+        <v>-1.1176</v>
       </c>
       <c r="G24" t="n">
         <v>-0.6442</v>
@@ -2326,13 +2326,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4133</v>
+        <v>-0.2304</v>
       </c>
       <c r="T24" t="n">
         <v>-0.0588</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3545</v>
+        <v>-0.1716</v>
       </c>
       <c r="V24" t="n">
         <v>-0.3018</v>
@@ -2359,22 +2359,22 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>8.493700000000002</v>
+        <v>9.7927</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.3474</v>
+        <v>-2.347500000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>10.8411</v>
+        <v>12.1403</v>
       </c>
       <c r="G25" t="n">
-        <v>6.932</v>
+        <v>6.931999999999999</v>
       </c>
       <c r="H25" t="n">
         <v>6.1747</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7573999999999994</v>
+        <v>0.7573999999999996</v>
       </c>
       <c r="J25" t="n">
         <v>4.424900000000001</v>
@@ -2383,16 +2383,16 @@
         <v>3.6702</v>
       </c>
       <c r="L25" t="n">
-        <v>0.7547000000000004</v>
+        <v>0.7547000000000003</v>
       </c>
       <c r="M25" t="n">
-        <v>2.5071</v>
+        <v>2.507099999999999</v>
       </c>
       <c r="N25" t="n">
         <v>2.5045</v>
       </c>
       <c r="O25" t="n">
-        <v>0.002600000000000158</v>
+        <v>0.002600000000000047</v>
       </c>
       <c r="P25" t="n">
         <v>1.887</v>
@@ -2404,13 +2404,13 @@
         <v>16.983</v>
       </c>
       <c r="S25" t="n">
-        <v>0.8818000000000001</v>
+        <v>2.1808</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3739</v>
+        <v>-0.3738</v>
       </c>
       <c r="U25" t="n">
-        <v>1.2557</v>
+        <v>2.5548</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2072</v>
